--- a/banking_application_forms/021_loan_estimate_form--banking_application_forms.xlsx
+++ b/banking_application_forms/021_loan_estimate_form--banking_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'weekly':_true}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'weekly': True}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'biweekly':_true}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'biweekly': True}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'monthly':_true}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'monthly': True}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'biannually':_true}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'biannually': True}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'annually':_true}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'annually': True}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'quarterly':_true}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'quarterly': True}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>home_equity</t>
+          <t>home equity</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>variable_plus_fees</t>
+          <t>variable plus fees</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>date of birth</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>date_of_death</t>
+          <t>date of death</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>date_of_mortgage</t>
+          <t>date of mortgage</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>date_of_sale</t>
+          <t>date of sale</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>non_linear</t>
+          <t>non linear</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>lump_sum</t>
+          <t>lump sum</t>
         </is>
       </c>
     </row>
